--- a/data/trans_orig/IP3111_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP3111_2023-Habitat-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8207</t>
+          <t>7190</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18737</t>
+          <t>18064</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>7926</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21212</t>
+          <t>22239</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17519</t>
+          <t>17304</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34749</t>
+          <t>35737</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14795</t>
+          <t>14802</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27666</t>
+          <t>27724</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17138</t>
+          <t>17503</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36371</t>
+          <t>35034</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34806</t>
+          <t>35209</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57602</t>
+          <t>57921</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,22%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23548</t>
+          <t>23160</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38137</t>
+          <t>38167</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19713</t>
+          <t>20098</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38854</t>
+          <t>39478</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>46902</t>
+          <t>47572</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>71782</t>
+          <t>71231</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,56%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10606</t>
+          <t>10549</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21543</t>
+          <t>21769</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16600</t>
+          <t>16722</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35738</t>
+          <t>35422</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30972</t>
+          <t>31656</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52338</t>
+          <t>52870</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,2%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10534</t>
+          <t>10268</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22275</t>
+          <t>22141</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7090</t>
+          <t>5558</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18811</t>
+          <t>17908</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>19185</t>
+          <t>18631</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>37282</t>
+          <t>37076</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12919</t>
+          <t>12685</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27419</t>
+          <t>26959</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17625</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>57963</t>
+          <t>56774</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>35159</t>
+          <t>34639</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>79148</t>
+          <t>82592</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>33,11%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16491</t>
+          <t>16078</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31601</t>
+          <t>31757</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17630</t>
+          <t>17553</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34468</t>
+          <t>33615</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>37249</t>
+          <t>36593</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>60236</t>
+          <t>60120</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20336</t>
+          <t>20082</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35793</t>
+          <t>36032</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>42983</t>
+          <t>41646</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67916</t>
+          <t>67439</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>68488</t>
+          <t>68996</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>97206</t>
+          <t>97968</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,74%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40347</t>
+          <t>40066</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64404</t>
+          <t>65884</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48995</t>
+          <t>49584</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>74756</t>
+          <t>74719</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>95764</t>
+          <t>93333</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>131357</t>
+          <t>130582</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,31%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24909</t>
+          <t>25470</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42162</t>
+          <t>43086</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29301</t>
+          <t>29899</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>50586</t>
+          <t>50707</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>60397</t>
+          <t>59553</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>87891</t>
+          <t>87468</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,31%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24026</t>
+          <t>23772</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>42413</t>
+          <t>42737</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32690</t>
+          <t>31453</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>61081</t>
+          <t>57656</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>60187</t>
+          <t>61432</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>93536</t>
+          <t>93698</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,75%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12480</t>
+          <t>11856</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26949</t>
+          <t>26882</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15741</t>
+          <t>16947</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32802</t>
+          <t>34458</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31475</t>
+          <t>31849</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52891</t>
+          <t>53451</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,41%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17198</t>
+          <t>16036</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>37904</t>
+          <t>38593</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15261</t>
+          <t>15494</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31171</t>
+          <t>30348</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>35863</t>
+          <t>37137</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>63923</t>
+          <t>63137</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,12%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16656</t>
+          <t>16593</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>41192</t>
+          <t>40768</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31404</t>
+          <t>31951</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>58196</t>
+          <t>57588</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>55509</t>
+          <t>51454</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>94672</t>
+          <t>92139</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>24,98%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17677</t>
+          <t>17485</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>40054</t>
+          <t>41073</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26701</t>
+          <t>26824</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>46793</t>
+          <t>46722</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>46918</t>
+          <t>48607</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>79839</t>
+          <t>82244</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>22,3%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>26529</t>
+          <t>24853</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>56472</t>
+          <t>57306</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>28410</t>
+          <t>29000</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>49415</t>
+          <t>51278</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>59068</t>
+          <t>59618</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>99945</t>
+          <t>99222</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,9%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16453</t>
+          <t>16651</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>96156</t>
+          <t>103890</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10364</t>
+          <t>10252</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23902</t>
+          <t>23974</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>31620</t>
+          <t>32636</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>141671</t>
+          <t>132949</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>36,05%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10261</t>
+          <t>9224</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25794</t>
+          <t>25249</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>15693</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>38374</t>
+          <t>38313</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>29093</t>
+          <t>28611</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>57176</t>
+          <t>56810</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21761</t>
+          <t>22000</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38808</t>
+          <t>39442</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19126</t>
+          <t>19355</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>36295</t>
+          <t>35791</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>45365</t>
+          <t>45145</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>68799</t>
+          <t>68820</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>26449</t>
+          <t>26611</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>43926</t>
+          <t>43954</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>29646</t>
+          <t>29446</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>48752</t>
+          <t>48548</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>60739</t>
+          <t>60765</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>87466</t>
+          <t>87511</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,6%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>21162</t>
+          <t>21737</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>38061</t>
+          <t>37971</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>32580</t>
+          <t>32341</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>52195</t>
+          <t>51686</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>60146</t>
+          <t>58662</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>86289</t>
+          <t>84673</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,77%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>20745</t>
+          <t>20986</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>36320</t>
+          <t>36112</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>14189</t>
+          <t>15594</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>31572</t>
+          <t>30992</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>38828</t>
+          <t>39330</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>61016</t>
+          <t>62143</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,18%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>12328</t>
+          <t>12119</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26186</t>
+          <t>26784</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>15478</t>
+          <t>15634</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>32835</t>
+          <t>33929</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>30807</t>
+          <t>32014</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>53551</t>
+          <t>55246</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>16,16%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>16905</t>
+          <t>17245</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>34571</t>
+          <t>35851</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>17164</t>
+          <t>17216</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>33933</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>38198</t>
+          <t>39265</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>61642</t>
+          <t>63803</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>77515</t>
+          <t>75474</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>110500</t>
+          <t>109000</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>72019</t>
+          <t>71916</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>103203</t>
+          <t>105058</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>156436</t>
+          <t>156966</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>202343</t>
+          <t>203756</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,65%</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>91458</t>
+          <t>90944</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>129554</t>
+          <t>131473</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>141526</t>
+          <t>140045</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>186054</t>
+          <t>186041</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>243091</t>
+          <t>241040</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>305736</t>
+          <t>301823</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,7%</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>119349</t>
+          <t>117069</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>162772</t>
+          <t>162562</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>146851</t>
+          <t>146559</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>189445</t>
+          <t>188540</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>277598</t>
+          <t>272879</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>339197</t>
+          <t>336200</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,17%</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4249,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>98230</t>
+          <t>100901</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>139265</t>
+          <t>141985</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>106512</t>
+          <t>107541</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>146789</t>
+          <t>145141</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>213906</t>
+          <t>216611</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>271758</t>
+          <t>271559</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>80089</t>
+          <t>79793</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>191499</t>
+          <t>192722</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>77547</t>
+          <t>76601</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>118360</t>
+          <t>116508</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>169208</t>
+          <t>172030</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>286309</t>
+          <t>280696</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -4475,12 +4475,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>64341</t>
+          <t>64296</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>96969</t>
+          <t>96381</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>82406</t>
+          <t>83954</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>141050</t>
+          <t>144583</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>156569</t>
+          <t>154387</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>224265</t>
+          <t>217996</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,67%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP3111_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP3111_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10637</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6032</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>17313</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8,66%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4,91%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>14,09%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>12175</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7190</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>18064</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>10,81%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,38%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>16,04%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13295</t>
+          <t>12004</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7926</t>
+          <t>7347</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22239</t>
+          <t>18587</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>25469</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17304</t>
+          <t>15934</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35737</t>
+          <t>31088</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24715</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>16241</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>34280</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>20,11%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>13,22%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>27,89%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>20371</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>14802</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>27724</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>18,09%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>13,14%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>24,62%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>25918</t>
+          <t>21676</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17503</t>
+          <t>15527</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35034</t>
+          <t>30190</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>46289</t>
+          <t>46391</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35209</t>
+          <t>36543</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57921</t>
+          <t>58223</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>24,25%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>26255</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>19023</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>36132</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>21,36%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>15,48%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>29,4%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>30147</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>23160</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>38167</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>26,77%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>20,57%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>33,89%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>28594</t>
+          <t>31474</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20098</t>
+          <t>23938</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39478</t>
+          <t>39212</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>58741</t>
+          <t>57729</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>47572</t>
+          <t>46524</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>71231</t>
+          <t>70256</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>29,26%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>24509</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>17226</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>34244</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>19,94%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>14,02%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>27,86%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>15584</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>10549</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>21769</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>13,84%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>9,37%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>19,33%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25311</t>
+          <t>16002</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16722</t>
+          <t>10928</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35422</t>
+          <t>22350</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>40895</t>
+          <t>40511</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31656</t>
+          <t>29915</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52870</t>
+          <t>50847</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,17%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11830</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6619</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>18595</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>9,63%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>5,39%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>15,13%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>15591</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>10268</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>22141</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>13,84%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,12%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>19,66%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11538</t>
+          <t>16019</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5558</t>
+          <t>10449</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17908</t>
+          <t>23634</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>27129</t>
+          <t>27849</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18631</t>
+          <t>19101</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>37076</t>
+          <t>36974</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -1285,72 +1285,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>24949</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>13565</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>46236</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>20,3%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>11,04%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>37,62%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>18746</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>12685</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>26959</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>16,65%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>11,26%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>23,94%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32160</t>
+          <t>20064</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>13314</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>56774</t>
+          <t>29519</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>50906</t>
+          <t>45013</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>34639</t>
+          <t>32968</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>82592</t>
+          <t>71912</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>29,95%</t>
         </is>
       </c>
     </row>
@@ -1398,74 +1398,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>112614</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>112614</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>112614</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>117238</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>117238</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>117238</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>136815</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>136815</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>136815</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>350</t>
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>249429</t>
+          <t>240134</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>249429</t>
+          <t>240134</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>249429</t>
+          <t>240134</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>22253</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>15279</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>30205</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>9,69%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>6,65%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>13,15%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>23306</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>16078</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>31757</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>12,62%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>8,7%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>17,19%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24901</t>
+          <t>23765</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17553</t>
+          <t>16604</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33615</t>
+          <t>32831</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>48207</t>
+          <t>46018</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>36593</t>
+          <t>36082</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>60120</t>
+          <t>57440</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,05%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>48419</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>38237</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>62824</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>21,08%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>16,64%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>27,35%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>27466</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>20082</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>36032</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>14,87%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>10,87%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>19,51%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>54112</t>
+          <t>27709</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>41646</t>
+          <t>20462</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67439</t>
+          <t>36434</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>81578</t>
+          <t>76128</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>68996</t>
+          <t>62763</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>97968</t>
+          <t>90869</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,23%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>56910</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>46577</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>69257</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>24,77%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>20,27%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>30,15%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>50643</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>40066</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>65884</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>27,42%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>21,69%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>35,67%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>60873</t>
+          <t>46471</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49584</t>
+          <t>36610</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>74719</t>
+          <t>57135</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,22 +1816,22 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>111516</t>
+          <t>103381</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>93333</t>
+          <t>88570</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>130582</t>
+          <t>119107</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>29,14%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>37650</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>29084</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>48877</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>16,39%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>12,66%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>21,28%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>33141</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>25470</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>43086</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>17,94%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>13,79%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>23,33%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>39775</t>
+          <t>32535</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29899</t>
+          <t>24758</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>50707</t>
+          <t>42371</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>72916</t>
+          <t>70185</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>59553</t>
+          <t>56813</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>87468</t>
+          <t>83114</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,34%</t>
         </is>
       </c>
     </row>
@@ -1967,72 +1967,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>41822</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>32068</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>56357</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>18,2%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>13,96%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>24,53%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>31915</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>23772</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>42737</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>17,28%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>12,87%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>23,14%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>43075</t>
+          <t>31385</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31453</t>
+          <t>23925</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>57656</t>
+          <t>40708</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>74990</t>
+          <t>73207</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>61432</t>
+          <t>59239</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>93698</t>
+          <t>87812</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,48%</t>
         </is>
       </c>
     </row>
@@ -2080,72 +2080,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>22681</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>14653</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>31004</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9,87%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>6,38%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>18238</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>11856</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>26882</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9,87%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>6,42%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>14,55%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>23324</t>
+          <t>17115</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16947</t>
+          <t>11481</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34458</t>
+          <t>25157</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>41562</t>
+          <t>39797</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31849</t>
+          <t>30486</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53451</t>
+          <t>51072</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,5%</t>
         </is>
       </c>
     </row>
@@ -2193,74 +2193,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>229735</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>229735</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>229735</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>268</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>184709</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>184709</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>184709</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>178979</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>178979</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>178979</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>246060</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>246060</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>246060</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>591</t>
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>430769</t>
+          <t>408715</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>430769</t>
+          <t>408715</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>430769</t>
+          <t>408715</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>19802</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>13927</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>27608</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>12,08%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>8,5%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>16,84%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>27831</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>16036</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>38593</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>14,78%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>8,52%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>20,5%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>22170</t>
+          <t>27722</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15494</t>
+          <t>20082</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>30348</t>
+          <t>36617</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>50001</t>
+          <t>47524</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>37137</t>
+          <t>38160</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>63137</t>
+          <t>59024</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>18,51%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>36670</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>26973</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>49116</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>22,37%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>16,46%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>29,97%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>28312</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>16593</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>40768</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>15,04%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>8,81%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>21,66%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>43328</t>
+          <t>23226</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31951</t>
+          <t>16743</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57588</t>
+          <t>31950</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>71640</t>
+          <t>59896</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>51454</t>
+          <t>49020</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>92139</t>
+          <t>76046</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>23,84%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>32953</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>24158</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>42593</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>20,1%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>14,74%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>25,99%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>29728</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>17485</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>41073</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>15,79%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>9,29%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>21,82%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>36149</t>
+          <t>29313</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26824</t>
+          <t>22228</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>46722</t>
+          <t>38593</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>65877</t>
+          <t>62266</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>48607</t>
+          <t>50816</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>82244</t>
+          <t>75678</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>23,73%</t>
         </is>
       </c>
     </row>
@@ -2649,72 +2649,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>36557</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>27547</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>47212</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>22,3%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>16,81%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>28,8%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>42460</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>24853</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>57306</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>22,56%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>13,2%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>30,44%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>38594</t>
+          <t>38229</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>29000</t>
+          <t>29768</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>51278</t>
+          <t>47531</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>81054</t>
+          <t>74787</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>59618</t>
+          <t>59980</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>99222</t>
+          <t>87209</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,34%</t>
         </is>
       </c>
     </row>
@@ -2767,32 +2767,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>42889</t>
+          <t>14709</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16651</t>
+          <t>9250</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>103890</t>
+          <t>23430</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2802,32 +2802,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>16335</t>
+          <t>19687</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10252</t>
+          <t>12943</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23974</t>
+          <t>29464</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>59225</t>
+          <t>34396</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32636</t>
+          <t>24923</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>132949</t>
+          <t>46836</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>14,68%</t>
         </is>
       </c>
     </row>
@@ -2875,72 +2875,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>23218</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>14811</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>37747</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>14,17%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>9,04%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>23,03%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>17028</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>9224</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>25249</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>9,05%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>13,41%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>23993</t>
+          <t>16861</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>10887</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>38313</t>
+          <t>24295</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>41021</t>
+          <t>40079</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>28611</t>
+          <t>29196</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>56810</t>
+          <t>54879</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>17,21%</t>
         </is>
       </c>
     </row>
@@ -2988,74 +2988,74 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>163910</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>163910</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>163910</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>155038</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>155038</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>155038</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>180569</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>180569</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>180569</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>442</t>
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>368818</t>
+          <t>318948</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>368818</t>
+          <t>318948</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>368818</t>
+          <t>318948</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>24726</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>17768</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>33388</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>14,88%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>10,69%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>20,09%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>29549</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>22000</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>39442</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>29457</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>22224</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>38149</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>17,96%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>13,37%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>23,97%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>26694</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>19355</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>35791</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>15,05%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>56243</t>
+          <t>54183</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>45145</t>
+          <t>44038</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>68820</t>
+          <t>66706</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,21%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>38477</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>30240</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>48531</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>23,16%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>18,2%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>29,21%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>34594</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>26611</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>43954</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>21,03%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>16,17%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>26,72%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>38815</t>
+          <t>34921</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>29446</t>
+          <t>26882</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>48548</t>
+          <t>44665</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>73409</t>
+          <t>73398</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>60765</t>
+          <t>60794</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>87511</t>
+          <t>86574</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>26,22%</t>
         </is>
       </c>
     </row>
@@ -3331,72 +3331,72 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>38499</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>29573</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>49043</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>23,17%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>17,8%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>29,51%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>29240</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>21737</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>37971</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>17,77%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>13,21%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>23,08%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>41735</t>
+          <t>30138</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>32341</t>
+          <t>22154</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>51686</t>
+          <t>39927</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>70975</t>
+          <t>68637</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>58662</t>
+          <t>55975</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>84673</t>
+          <t>80894</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,5%</t>
         </is>
       </c>
     </row>
@@ -3444,72 +3444,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>20091</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>13573</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>28115</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>12,09%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>8,17%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>16,92%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>28019</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>20986</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>36112</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>17,03%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>12,76%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>21,95%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>21788</t>
+          <t>27525</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>15594</t>
+          <t>19917</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>30992</t>
+          <t>35486</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>49807</t>
+          <t>47617</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>39330</t>
+          <t>36803</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>62143</t>
+          <t>57962</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>17,56%</t>
         </is>
       </c>
     </row>
@@ -3557,72 +3557,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>20227</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>13169</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>27721</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>12,17%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>7,93%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>16,68%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>18529</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>12119</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>26784</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>11,26%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>7,37%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>16,28%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>23411</t>
+          <t>18586</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>15634</t>
+          <t>12211</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>33929</t>
+          <t>26237</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>41940</t>
+          <t>38814</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>32014</t>
+          <t>29382</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>55246</t>
+          <t>50063</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -3670,72 +3670,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>24145</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>17164</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>33403</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>14,53%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>10,33%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>20,1%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>24588</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>17245</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>35851</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>14,95%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>10,48%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>21,79%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>24867</t>
+          <t>23350</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>17216</t>
+          <t>16852</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>33933</t>
+          <t>32204</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>49455</t>
+          <t>47496</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>39265</t>
+          <t>37709</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>63803</t>
+          <t>60122</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,21%</t>
         </is>
       </c>
     </row>
@@ -3783,74 +3783,74 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>163979</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>163979</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>163979</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="P31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>177309</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>177309</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>177309</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>467</t>
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3900,72 +3900,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>77418</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>64065</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>93351</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>11,34%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>9,38%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>13,67%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>92862</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>75474</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>109000</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>14,28%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>11,61%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>16,77%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>87059</t>
+          <t>92948</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>71916</t>
+          <t>79007</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>105058</t>
+          <t>109340</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>179921</t>
+          <t>170365</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>156966</t>
+          <t>151963</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>203756</t>
+          <t>192118</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,8%</t>
         </is>
       </c>
     </row>
@@ -4013,72 +4013,72 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>148281</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>128968</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>170691</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>21,72%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>18,89%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>110744</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>90944</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>131473</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>17,04%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>13,99%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>20,22%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>162173</t>
+          <t>107532</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>140045</t>
+          <t>92789</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>186041</t>
+          <t>124292</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,32 +4088,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>272917</t>
+          <t>255813</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>241040</t>
+          <t>232392</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>301823</t>
+          <t>281777</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,71%</t>
         </is>
       </c>
     </row>
@@ -4126,67 +4126,67 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>154617</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>135943</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>174878</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>22,65%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>19,91%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>25,62%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>139758</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>117069</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>162562</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>21,5%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>18,01%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>25,01%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>167350</t>
+          <t>137396</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>146559</t>
+          <t>119573</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>188540</t>
+          <t>156565</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>307108</t>
+          <t>292014</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>272879</t>
+          <t>264564</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>336200</t>
+          <t>317460</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -4239,72 +4239,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>118808</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>101422</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>138677</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>17,4%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>14,86%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>20,31%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>169</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>119203</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>100901</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>141985</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>18,34%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>15,52%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>21,84%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>125468</t>
+          <t>114291</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>107541</t>
+          <t>98119</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>145141</t>
+          <t>130048</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>244671</t>
+          <t>233099</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>216611</t>
+          <t>208855</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>271559</t>
+          <t>260088</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>20,04%</t>
         </is>
       </c>
     </row>
@@ -4352,72 +4352,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>88589</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>71123</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>108099</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>12,98%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>10,42%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>15,83%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>108924</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>79793</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>192722</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>16,76%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>12,27%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>29,65%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>94359</t>
+          <t>85677</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>76601</t>
+          <t>72650</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>116508</t>
+          <t>102630</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>203283</t>
+          <t>174266</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>172030</t>
+          <t>151396</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>280696</t>
+          <t>196601</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -4465,72 +4465,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>94993</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>76356</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>123374</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>13,91%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>11,18%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>18,07%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>78600</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>64296</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>96381</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>12,09%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>9,89%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>14,83%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>104343</t>
+          <t>77390</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>83954</t>
+          <t>63483</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>144583</t>
+          <t>93265</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>182943</t>
+          <t>172384</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>154387</t>
+          <t>149731</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>217996</t>
+          <t>203185</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,65%</t>
         </is>
       </c>
     </row>
@@ -4578,74 +4578,74 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>938</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>682707</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>682707</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>682707</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>912</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>650092</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>650092</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>650092</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>615235</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>615235</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>615235</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="P38" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>938</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>740752</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>740752</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>740752</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
           <t>1850</t>
@@ -4653,17 +4653,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1390844</t>
+          <t>1297941</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1390844</t>
+          <t>1297941</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1390844</t>
+          <t>1297941</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
